--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR2012</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`accademic` (en)</t>
+          <t>`emily` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GAR2HR</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,24 +509,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`lässtilar` (sv)</t>
+          <t>`hanan` (en)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`htat` (en)</t>
+          <t>`idris` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`selction` (en)</t>
+          <t>`muhammed` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`criticially` (en)</t>
+          <t>`murr` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`oligatory` (en)</t>
+          <t>`nasrallah` (en)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,51 +649,51 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`ttheir` (en)</t>
+          <t>`yousef` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`zakaria` (en)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>AR1004</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -703,51 +703,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`froming` (en)</t>
+          <t>`hec` (en)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>AR1007</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`ochspanskspråkiga` (sv)</t>
+          <t>`roleplays` (en)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>AR1009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`analye` (en)</t>
+          <t>`roleplays` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`roleplays` (en)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`coomprising` (en)</t>
+          <t>`syriand` (en)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -838,51 +838,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`sidor` (en)</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EN3076</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,51 +892,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`balahga` (en)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,78 +973,78 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`stilistic` (en)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`accademic` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GAR2HR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,51 +1054,51 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`lässtilar` (sv)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GAR39K</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`htat` (en)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GAR39L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`selction` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`criticially` (en)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`oligatory` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`ttheir` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,56 +1211,56 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`franskämnets` (sv)</t>
+          <t>`froming` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,51 +1270,51 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`franskämnets` (sv)</t>
+          <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AFR26R</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`främmandespråksinlärning` (sv)</t>
+          <t>`poststructuralism` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`analye` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,51 +1351,51 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`engelskämnet` (sv)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,51 +1405,51 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`franskämnets` (sv)</t>
+          <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`engelskämnet` (sv)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,78 +1459,78 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`irish` (en)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`poststructuralism` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`coomprising` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,51 +1540,51 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`sidor` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`låneord` (sv)</t>
+          <t>`historicism` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`poststructuralism` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,51 +1621,51 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>EN3076</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,186 +1675,186 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`affärsmötesrollspel` (sv)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`främmandespråksforskning` (sv)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GKI3GQ</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`aper` (en)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GPR279</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,78 +1864,78 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`närstudium` (sv)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GPR2X9</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`närstudium` (sv)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,51 +1945,51 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`närstudium` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,105 +2053,105 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`achiev` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`franskämnets` (sv)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`franskämnets` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>AFR26R</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`främmandespråksinlärning` (sv)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,159 +2161,159 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`spanskämnets` (sv)</t>
+          <t>`authorships` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`spanskämnets` (sv)</t>
+          <t>`maghreb` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`spanskämnets` (sv)</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`forsättning` (sv)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,51 +2350,51 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`franskämnets` (sv)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,51 +2404,51 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,51 +2485,51 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`reserach` (en)</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,78 +2566,78 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`transspråkande` (sv)</t>
+          <t>`låneord` (sv)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSS2BZ</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`litteracitetsområdet` (sv)</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`litteracitetsområdet` (sv)</t>
+          <t>`contextualise` (en)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`studenta` (en)</t>
+          <t>`sardinia` (en)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`sicily` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,51 +2728,51 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`iii-nivå` (sv)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,78 +2782,78 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSV2P9</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,78 +2863,78 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`exeptions` (en)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`devleopment` (en)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,78 +2944,78 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`wikipedia` (en)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`acheive` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,186 +3025,186 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`standardnära` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`confucianism` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`högstadie` (sv)</t>
+          <t>`taoism` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GKI2VM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`främmandespråksforskning` (sv)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GKI3GQ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`aper` (en)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`tyskämnet` (sv)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`samhällssyttringar` (sv)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,105 +3241,105 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`tyskämnet` (sv)</t>
+          <t>`läsintryck` (sv)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`tilllämpa` (sv)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GTY3J7</t>
+          <t>GPR279</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`aachieve` (en)</t>
+          <t>`närstudium` (sv)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR279</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`tyskämnet` (sv)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GPR2X9</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`närstudium` (sv)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`creits` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TY3010</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`tyskämnets` (sv)</t>
+          <t>`närstudium` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`brign` (en)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`othe` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,44 +3484,2096 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`rmedia` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>ARY23F</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`stalin` (en)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ARY25M</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`blogosphere` (en)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GRY28J</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`achiev` (en)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GRY28U</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`formualte` (en)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`assessement` (en)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`obilgatory` (en)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>GRY2LE</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`sccholarly` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>GRY36G</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`onwards` (en)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>GRY37X</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`systematised` (en)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GRY38S</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`läsförståesle` (sv)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GSP2KS</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>`förtjänstersåväl` (sv)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>`ställdakrav` (sv)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>`tidsramargenomföra` (sv)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>`vilarpå` (sv)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>SP1050</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>`assigments` (en)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>`realtion` (en)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>`semantical` (en)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>`communciation` (en)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>`reserach` (en)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>ASS26C</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>`transspråkande` (sv)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GSS2GP</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>`lärsituation` (sv)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GSS2GP</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>`lärsituationer` (sv)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>`pracitse` (en)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>`jämörs` (sv)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>`lärsituation` (sv)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GSS39U</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>`ochförhållningssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BH</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>`studenta` (en)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BH</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>`writtem` (en)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BH</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>`writtten` (en)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>`framställing` (sv)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>`refelction` (en)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>`tillfredställande` (sv)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>`witten` (en)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>`näbaserade` (sv)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>`änvänder` (sv)</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>`inlärartal` (sv)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>`affrican` (en)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>`centrual` (en)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>`dealrs` (en)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>`dourse` (en)</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>`egarding` (en)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>`hec` (en)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>`langue` (en)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>`prespectives` (en)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>`relatec` (en)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>`researchj` (en)</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>`teorritoriality` (en)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>`användingen` (sv)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>SS3009</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>`skriftspråksanvänding` (sv)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>`läsmiljöns` (sv)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>`devleopment` (en)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>`läsmiljöns` (sv)</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>`tiilämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>`närstudiet` (sv)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>`standardnära` (sv)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>`verbalspråket` (sv)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DF</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>`högstadie` (sv)</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>`additon` (en)</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>`schlarly` (en)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CT</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>`tyskämnet` (sv)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>`samhällssyttringar` (sv)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>`tyskämnet` (sv)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>`tilllämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J7</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>`aachieve` (en)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J9</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>`tyskämnet` (sv)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>`creits` (en)</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>TY3010</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>`tyskämnets` (sv)</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>`brign` (en)</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
         <is>
           <t>`assingments` (en)</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E114"/>
+  <autoFilter ref="A1:E190"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3749,6 +5801,158 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AR1007</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`roleplays` (en)</t>
+          <t>`syriand` (en)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AR1009</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`roleplays` (en)</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,24 +779,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`roleplays` (en)</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`syriand` (en)</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`proficiencythrough` (en)</t>
+          <t>`balahga` (en)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`assesment` (en)</t>
+          <t>`stilistic` (en)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`balahga` (en)</t>
+          <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`diffrent` (en)</t>
+          <t>`accademic` (en)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>GAR39K</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`stilistic` (en)</t>
+          <t>`htat` (en)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>GAR39L</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,29 +995,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`inlämmningsuppgifter` (sv)</t>
+          <t>`selction` (en)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AR2012</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,51 +1027,51 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`accademic` (en)</t>
+          <t>`criticially` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GAR2HR</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`lässtilar` (sv)</t>
+          <t>`oligatory` (en)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2HR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,46 +1081,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`htat` (en)</t>
+          <t>`ttheir` (en)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`selction` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`criticially` (en)</t>
+          <t>`froming` (en)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`oligatory` (en)</t>
+          <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`ttheir` (en)</t>
+          <t>`analye` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`froming` (en)</t>
+          <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`ochspanskspråkiga` (sv)</t>
+          <t>`irish` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`poststructuralism` (en)</t>
+          <t>`coomprising` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`analye` (en)</t>
+          <t>`sidor` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`historicism` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`engelskämnet` (sv)</t>
+          <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`ämnesdidaktiskområde` (sv)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>EN3076</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`engelskämnet` (sv)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`irish` (en)</t>
+          <t>`affärsmötesrollspel` (sv)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`poststructuralism` (en)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`coomprising` (en)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`sidor` (en)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`historicism` (en)</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`poststructuralism` (en)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`samtidafrågor` (sv)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EN3076</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`affärsmötesrollspel` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR26R</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,78 +1837,78 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`främmandespråksinlärning` (sv)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`authorships` (en)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,51 +1945,51 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`maghreb` (en)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,51 +1999,51 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`forsättning` (sv)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`franskämnets` (sv)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`franskämnets` (sv)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AFR26R</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`främmandespråksinlärning` (sv)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,29 +2183,29 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,78 +2215,78 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`authorships` (en)</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`maghreb` (en)</t>
+          <t>`låneord` (sv)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,78 +2296,78 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`orbally` (en)</t>
+          <t>`contextualise` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`forsättning` (sv)</t>
+          <t>`sardinia` (en)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`franskämnets` (sv)</t>
+          <t>`sicily` (en)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,51 +2377,51 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,105 +2431,105 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`iii-nivå` (sv)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`teachning` (en)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,105 +2539,105 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`låneord` (sv)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`contextualise` (en)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`sardinia` (en)</t>
+          <t>`wikipedia` (en)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,105 +2674,105 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`sicily` (en)</t>
+          <t>`acheive` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`confucianism` (en)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`iii-nivå` (sv)</t>
+          <t>`taoism` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GKI2VM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,51 +2782,51 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`främmandespråksforskning` (sv)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GKI3GQ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,78 +2836,78 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`aper` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,78 +2917,78 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`läsintryck` (sv)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`wikipedia` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,51 +2998,51 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`acheive` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`confucianism` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,78 +3079,78 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`taoism` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`främmandespråksforskning` (sv)</t>
+          <t>`stalin` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`blogosphere` (en)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GKI3GQ</t>
+          <t>GRY28J</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3160,105 +3160,105 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`aper` (en)</t>
+          <t>`achiev` (en)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`läsintryck` (sv)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,132 +3268,132 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GPR279</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`närstudium` (sv)</t>
+          <t>`systematised` (en)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR279</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GPR2X9</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`närstudium` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,78 +3403,78 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`närstudium` (sv)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`stalin` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`blogosphere` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`achiev` (en)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3619,105 +3619,105 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`reserach` (en)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`transspråkande` (sv)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`onwards` (en)</t>
+          <t>`lärsituationer` (sv)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3727,78 +3727,78 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`systematised` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3835,105 +3835,105 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3943,51 +3943,51 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3997,73 +3997,73 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`reserach` (en)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`transspråkande` (sv)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4100,24 +4100,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4127,24 +4127,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`lärsituationer` (sv)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4159,19 +4159,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4208,24 +4208,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4235,24 +4235,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`hec` (en)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4262,24 +4262,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`langue` (en)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`studenta` (en)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4321,19 +4321,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4348,19 +4348,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4370,24 +4370,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4397,24 +4397,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4429,78 +4429,78 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`devleopment` (en)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,159 +4537,159 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`standardnära` (sv)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`högstadie` (sv)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`hec` (en)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4726,105 +4726,105 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`langue` (en)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GTY3J7</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4834,24 +4834,24 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`aachieve` (en)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4861,78 +4861,78 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4942,638 +4942,71 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>`devleopment` (en)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>`närstudiet` (sv)</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>`standardnära` (sv)</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>`verbalspråket` (sv)</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DF</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>`högstadie` (sv)</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>GSV3FP</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>`framåtsiktande` (sv)</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>ATY2B8</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>`additon` (en)</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>ATY2B8</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>`schlarly` (en)</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>GTY2N5</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CT</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>`tyskämnet` (sv)</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>`samhällssyttringar` (sv)</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>`tyskämnet` (sv)</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J5</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>`tilllämpa` (sv)</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J7</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>`aachieve` (en)</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>`tyskämnet` (sv)</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>`creits` (en)</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>TY3010</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>`tyskämnets` (sv)</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>`brign` (en)</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>`othe` (en)</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>`rmedia` (en)</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E190"/>
+  <autoFilter ref="A1:E169"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -5911,48 +5344,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$169</definedName>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`emily` (en)</t>
+          <t>`syriand` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,19 +514,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`hanan` (en)</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,24 +536,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`idris` (en)</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`muhammed` (en)</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`murr` (en)</t>
+          <t>`balahga` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`nasrallah` (en)</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`yousef` (en)</t>
+          <t>`stilistic` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AR1003</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`zakaria` (en)</t>
+          <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AR1004</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`hec` (en)</t>
+          <t>`accademic` (en)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>GAR39K</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`syriand` (en)</t>
+          <t>`htat` (en)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>GAR39L</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,51 +757,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`proficiencythrough` (en)</t>
+          <t>`selction` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`criticially` (en)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`assesment` (en)</t>
+          <t>`oligatory` (en)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -838,51 +838,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`balahga` (en)</t>
+          <t>`ttheir` (en)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`diffrent` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`stilistic` (en)</t>
+          <t>`froming` (en)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`inlämmningsuppgifter` (sv)</t>
+          <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AR2012</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`accademic` (en)</t>
+          <t>`analye` (en)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,46 +973,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`htat` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`selction` (en)</t>
+          <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`criticially` (en)</t>
+          <t>`irish` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`oligatory` (en)</t>
+          <t>`coomprising` (en)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`ttheir` (en)</t>
+          <t>`sidor` (en)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`historicism` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`froming` (en)</t>
+          <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`ochspanskspråkiga` (sv)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>EN3076</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`analye` (en)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`affärsmötesrollspel` (sv)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`ämnesdidaktiskområde` (sv)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`irish` (en)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`coomprising` (en)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`sidor` (en)</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`historicism` (en)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`samtidafrågor` (sv)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EN3076</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`affärsmötesrollspel` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR26R</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,78 +1594,78 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`främmandespråksinlärning` (sv)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`authorships` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,51 +1702,51 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`maghreb` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,51 +1756,51 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`forsättning` (sv)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AFR26R</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`främmandespråksinlärning` (sv)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`authorships` (en)</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,110 +1940,110 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`maghreb` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`orbally` (en)</t>
+          <t>`låneord` (sv)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`forsättning` (sv)</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`contextualise` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,51 +2080,51 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`sardinia` (en)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GIT2TJ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`sicily` (en)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,51 +2134,51 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`teachning` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,51 +2188,51 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`iii-nivå` (sv)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`låneord` (sv)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`contextualise` (en)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,132 +2323,132 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`sardinia` (en)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`sicily` (en)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`wikipedia` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`iii-nivå` (sv)</t>
+          <t>`acheive` (en)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,51 +2458,51 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`confucianism` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GKI2VL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,154 +2512,154 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`taoism` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GKI2VM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`främmandespråksforskning` (sv)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>GKI3GQ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`aper` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`wikipedia` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`acheive` (en)</t>
+          <t>`läsintryck` (sv)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,56 +2696,56 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`confucianism` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,78 +2755,78 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`taoism` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`främmandespråksforskning` (sv)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GKI3GQ</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,105 +2836,105 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`aper` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`stalin` (en)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>ARY25M</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`blogosphere` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GRY28J</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`läsintryck` (sv)</t>
+          <t>`achiev` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GRY37X</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,51 +3052,51 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`systematised` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,132 +3106,132 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`stalin` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`blogosphere` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`achiev` (en)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,46 +3295,46 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`systematised` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3371,29 +3371,29 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`reserach` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`transspråkande` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`lärsituationer` (sv)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,105 +3511,105 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`reserach` (en)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3641,24 +3641,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`transspråkande` (sv)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3673,19 +3673,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3695,24 +3695,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`lärsituationer` (sv)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3722,24 +3722,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,19 +3889,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3911,24 +3911,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,24 +3965,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`langue` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4019,24 +4019,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4046,17 +4046,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
@@ -4073,12 +4073,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -4117,7 +4117,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4127,24 +4127,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4154,56 +4154,56 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,186 +4213,186 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`devleopment` (en)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`hec` (en)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`langue` (en)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`standardnära` (sv)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`högstadie` (sv)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,105 +4402,105 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`devleopment` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,51 +4537,51 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3J7</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`aachieve` (en)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,100 +4591,100 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`standardnära` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`högstadie` (sv)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4699,19 +4699,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,287 +4726,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>GTY2N5</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>`samhällssyttringar` (sv)</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J5</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>`tilllämpa` (sv)</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J7</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>`aachieve` (en)</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>`creits` (en)</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>`brign` (en)</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>`othe` (en)</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>`rmedia` (en)</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E169"/>
+  <autoFilter ref="A1:E159"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -5324,26 +5054,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`balahga` (en)</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`diffrent` (en)</t>
+          <t>`stilistic` (en)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -644,24 +644,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`stilistic` (en)</t>
+          <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`inlämmningsuppgifter` (sv)</t>
+          <t>`accademic` (en)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AR2012</t>
+          <t>GAR39K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`accademic` (en)</t>
+          <t>`htat` (en)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>GAR39L</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`htat` (en)</t>
+          <t>`selction` (en)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`selction` (en)</t>
+          <t>`criticially` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`criticially` (en)</t>
+          <t>`oligatory` (en)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`oligatory` (en)</t>
+          <t>`ttheir` (en)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,17 +833,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`ttheir` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`froming` (en)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`froming` (en)</t>
+          <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`ochspanskspråkiga` (sv)</t>
+          <t>`analye` (en)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`analye` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`ämnesdidaktiskområde` (sv)</t>
+          <t>`coomprising` (en)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EN3029</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`irish` (en)</t>
+          <t>`historicism` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`coomprising` (en)</t>
+          <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`sidor` (en)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>EN3076</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`historicism` (en)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`samtidafrågor` (sv)</t>
+          <t>`affärsmötesrollspel` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EN3076</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`affärsmötesrollspel` (sv)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,51 +1486,51 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>AFR26R</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`främmandespråksinlärning` (sv)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AFR26R</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`främmandespråksinlärning` (sv)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`forsättning` (sv)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`authorships` (en)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`maghreb` (en)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`orbally` (en)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`forsättning` (sv)</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`låneord` (sv)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,46 +1918,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`teachning` (en)</t>
+          <t>`contextualise` (en)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,29 +1967,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,51 +1999,51 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`låneord` (sv)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`contextualise` (en)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`sardinia` (en)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIT2TJ</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,51 +2107,51 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`sicily` (en)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,51 +2161,51 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>AKI28Y</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`iii-nivå` (sv)</t>
+          <t>`acheive` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GKI2VM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,51 +2242,51 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`främmandespråksforskning` (sv)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GKI3GQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,51 +2296,51 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`aper` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`läsintryck` (sv)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,78 +2404,78 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`wikipedia` (en)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`acheive` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`confucianism` (en)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GKI2VL</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,78 +2512,78 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`taoism` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`främmandespråksforskning` (sv)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>GRY28J</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`achiev` (en)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GKI3GQ</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,267 +2593,267 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`aper` (en)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`läsintryck` (sv)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`stalin` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ARY25M</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`blogosphere` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY25M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`achiev` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,105 +2998,105 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`reserach` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GRY37X</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`systematised` (en)</t>
+          <t>`lärsituationer` (sv)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY37X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,51 +3187,51 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,51 +3241,51 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,51 +3295,51 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,46 +3349,46 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`reserach` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`transspråkande` (sv)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3452,24 +3452,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`lärsituationer` (sv)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3511,19 +3511,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3560,24 +3560,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3587,24 +3587,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3668,24 +3668,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3695,24 +3695,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3727,78 +3727,78 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`devleopment` (en)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3835,132 +3835,132 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`högstadie` (sv)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3997,105 +3997,105 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`langue` (en)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GTY3J7</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`aachieve` (en)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4132,78 +4132,78 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,530 +4213,71 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`devleopment` (en)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>`närstudiet` (sv)</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>`standardnära` (sv)</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>`verbalspråket` (sv)</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DF</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>`högstadie` (sv)</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>GSV3FP</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>`framåtsiktande` (sv)</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>ATY2B8</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>`additon` (en)</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>ATY2B8</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>`schlarly` (en)</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>GTY2N5</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>`samhällssyttringar` (sv)</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J5</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>`tilllämpa` (sv)</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J7</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>`aachieve` (en)</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>`creits` (en)</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>`brign` (en)</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>`othe` (en)</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>`rmedia` (en)</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E159"/>
+  <autoFilter ref="A1:E142"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -5020,40 +4561,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR1012</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,56 +482,56 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`syriand` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -541,71 +541,3743 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>AR2001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`diffrent` (en)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AR2009</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`stilistic` (en)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AR2010</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`inlämmningsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>AR2012</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`accademic` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GAR39K</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`htat` (en)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GAR39L</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`selction` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AEN252</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`criticially` (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AEN252</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`oligatory` (en)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AEN25S</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`ttheir` (en)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`europeiskspråkiga` (sv)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`froming` (en)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BZ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`ochspanskspråkiga` (sv)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>EN2028</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`analye` (en)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>EN2043</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`knowlege` (en)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EN2046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`ämnesdidaktiskområde` (sv)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>EN3063</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`coomprising` (en)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>EN3064</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`historicism` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>EN3071</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`samtidafrågor` (sv)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>EN3075</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`vgs` (en)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>EN3076</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`vgs` (en)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GEN2HB</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`affärsmötesrollspel` (sv)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GEN33R</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`förseminarieupgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`beteen` (en)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`devlopment` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GEN3BQ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`intepreted` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`bedöming` (sv)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`föväntas` (sv)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`ideströmningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DG</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`literarature` (en)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DJ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`anlyses` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`anlyses` (en)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`indepently` (en)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`knowlege` (en)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`literarature` (en)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AFR26R</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`främmandespråksinlärning` (sv)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`percieving` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GFR2A8</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GFR2HZ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`orbally` (en)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GFR2W9</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`forsättning` (sv)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`defens` (en)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`ehtics` (en)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`godänd` (sv)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`ehtics` (en)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`teachning` (en)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HN</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`godänd` (sv)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GIT2A3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`indentify` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GIT2AE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`låneord` (sv)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GIT2AE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`particicpation` (en)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TH</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`contextualise` (en)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TK</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`themself` (en)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GIT2Y8</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`nlämningsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AJP26Z</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`europeiskspråkiga` (sv)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GJP23S</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`språkfärdiget` (sv)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GJP2MZ</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`opprtunity` (en)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GJP37U</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>`sritten` (en)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GJP37W</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`featuers` (en)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GJP39V</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`utanförperspektiv` (sv)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>JP1045</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`gundläggande` (sv)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>AKI28Y</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`acheive` (en)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GKI2PY</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`forsätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GKI2VM</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`främmandespråksforskning` (sv)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CB</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GKI3GQ</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`aper` (en)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>KI1030</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>KI1043</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>KI1043</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`läsintryck` (sv)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>KI1051</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`textsabout` (en)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
           <t>GPR2W2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`tha` (en)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>PR2003</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`thsi` (en)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>PR2004</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`prinicipe` (en)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>PR2005</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`credis` (en)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GRY28J</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`achiev` (en)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GRY28U</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`formualte` (en)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`assessement` (en)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`obilgatory` (en)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GRY2LE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`sccholarly` (en)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GRY38S</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`läsförståesle` (sv)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GSP2KS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`förtjänstersåväl` (sv)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>`ställdakrav` (sv)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>`tidsramargenomföra` (sv)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`vilarpå` (sv)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SP1050</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`assigments` (en)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`realtion` (en)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`semantical` (en)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`communciation` (en)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`reserach` (en)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GSS2GP</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`lärsituation` (sv)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GSS2GP</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`lärsituationer` (sv)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`pracitse` (en)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`jämörs` (sv)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`lärsituation` (sv)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GSS39U</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`ochförhållningssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BH</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`writtem` (en)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BH</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`writtten` (en)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`framställing` (sv)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`refelction` (en)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`tillfredställande` (sv)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`witten` (en)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`näbaserade` (sv)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`änvänder` (sv)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`inlärartal` (sv)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`affrican` (en)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`centrual` (en)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`dealrs` (en)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`dourse` (en)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`egarding` (en)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`prespectives` (en)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`relatec` (en)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`researchj` (en)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`teorritoriality` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`användingen` (sv)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>SS3009</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`skriftspråksanvänding` (sv)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`läsmiljöns` (sv)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>`devleopment` (en)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>`läsmiljöns` (sv)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>`tiilämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>`närstudiet` (sv)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>`verbalspråket` (sv)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DF</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>`högstadie` (sv)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>`additon` (en)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>`schlarly` (en)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>`samhällssyttringar` (sv)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>`tilllämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J7</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>`aachieve` (en)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>`creits` (en)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>`brign` (en)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>TY3016</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>`assingments` (en)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E142"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -617,6 +4289,278 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3739,7 +3739,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3776,24 +3776,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`devleopment` (en)</t>
+          <t>`läsförkunskaper` (sv)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3857,24 +3857,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`devleopment` (en)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,19 +3889,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3916,19 +3916,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`högstadie` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,78 +3943,78 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`högstadie` (sv)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4024,19 +4024,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4046,24 +4046,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`samhällssyttringar` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4073,24 +4073,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`tilllämpa` (sv)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GTY3J7</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4100,24 +4100,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`aachieve` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4154,24 +4154,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`creits` (en)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>GTY3J7</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`brign` (en)</t>
+          <t>`aachieve` (en)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4208,24 +4208,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`othe` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4240,44 +4240,125 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`rmedia` (en)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>`brign` (en)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
         <is>
           <t>`assingments` (en)</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E142"/>
+  <autoFilter ref="A1:E145"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4561,6 +4642,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1066,7 +1066,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`affärsmötesrollspel` (sv)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>EN3076</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`affärsmötesrollspel` (sv)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>AFR26R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`främmandespråksinlärning` (sv)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AFR26R</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`främmandespråksinlärning` (sv)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`forsättning` (sv)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`orbally` (en)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`forsättning` (sv)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1751,29 +1751,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`teachning` (en)</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`låneord` (sv)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`låneord` (sv)</t>
+          <t>`contextualise` (en)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,56 +1913,56 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`contextualise` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,29 +2102,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GKI2VM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`främmandespråksforskning` (sv)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AKI28Y</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`acheive` (en)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI28Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`främmandespråksforskning` (sv)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`läsintryck` (sv)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GKI3GQ</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`aper` (en)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,78 +2323,78 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`läsintryck` (sv)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,29 +2426,29 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GRY28J</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,29 +2561,29 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`achiev` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,105 +2593,105 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2733,14 +2733,14 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,83 +2831,83 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`lärsituationer` (sv)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,73 +2944,73 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`reserach` (en)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,24 +3047,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`lärsituationer` (sv)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,24 +3155,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3209,24 +3209,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3236,24 +3236,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3263,24 +3263,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3317,24 +3317,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3371,24 +3371,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,164 +3533,164 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`läsförkunskaper` (sv)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`läsförkunskaper` (sv)</t>
+          <t>`högstadie` (sv)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3813,46 +3813,46 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`devleopment` (en)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3970,73 +3970,73 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`högstadie` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4100,265 +4100,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>`samhällssyttringar` (sv)</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J5</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>`tilllämpa` (sv)</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J7</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>`aachieve` (en)</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>`creits` (en)</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>`brign` (en)</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>`othe` (en)</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>`rmedia` (en)</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E145"/>
+  <autoFilter ref="A1:E136"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4630,24 +4387,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1012,7 +1012,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`historicism` (en)</t>
+          <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`samtidafrågor` (sv)</t>
+          <t>`affärsmötesrollspel` (sv)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`affärsmötesrollspel` (sv)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,46 +1405,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>AFR26R</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`främmandespråksinlärning` (sv)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AFR26R</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`främmandespråksinlärning` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`orbally` (en)</t>
+          <t>`forsättning` (sv)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`forsättning` (sv)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,51 +1724,51 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`teachning` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`låneord` (sv)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`låneord` (sv)</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`contextualise` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`contextualise` (en)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,29 +1886,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI2VM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`främmandespråksforskning` (sv)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`främmandespråksforskning` (sv)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,17 +2210,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`läsintryck` (sv)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,51 +2264,51 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`läsintryck` (sv)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2534,51 +2534,51 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,39 +2809,39 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`lärsituationer` (sv)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`lärsituationer` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,17 +2939,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`lärsituation` (sv)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3020,24 +3020,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,17 +3155,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3479,24 +3479,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`läsförkunskaper` (sv)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`läsförkunskaper` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`läsmiljöns` (sv)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`högstadie` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,39 +3781,39 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`högstadie` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3857,24 +3857,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,19 +3889,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3916,19 +3916,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`samhällssyttringar` (sv)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`tilllämpa` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,24 +3965,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`creits` (en)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`brign` (en)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`othe` (en)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,44 +4078,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`rmedia` (en)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E136"/>
+  <autoFilter ref="A1:E135"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4385,8 +4358,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR1012</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`syriand` (en)</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`proficiencythrough` (en)</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`assesment` (en)</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`diffrent` (en)</t>
+          <t>`stilistic` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -617,24 +617,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`stilistic` (en)</t>
+          <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -644,24 +644,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`inlämmningsuppgifter` (sv)</t>
+          <t>`accademic` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AR2012</t>
+          <t>GAR39K</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`accademic` (en)</t>
+          <t>`htat` (en)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>GAR39L</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`htat` (en)</t>
+          <t>`selction` (en)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`selction` (en)</t>
+          <t>`criticially` (en)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`criticially` (en)</t>
+          <t>`oligatory` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`oligatory` (en)</t>
+          <t>`ttheir` (en)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`ttheir` (en)</t>
+          <t>`froming` (en)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`froming` (en)</t>
+          <t>`analye` (en)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`ochspanskspråkiga` (sv)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`analye` (en)</t>
+          <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`coomprising` (en)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`ämnesdidaktiskområde` (sv)</t>
+          <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`coomprising` (en)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`samtidafrågor` (sv)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`affärsmötesrollspel` (sv)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,46 +1378,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AFR26R</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`främmandespråksinlärning` (sv)</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR26R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`forsättning` (sv)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`orbally` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`forsättning` (sv)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,56 +1616,56 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GIT2TH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,46 +1702,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`teachning` (en)</t>
+          <t>`contextualise` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1751,29 +1751,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`låneord` (sv)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`contextualise` (en)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,321 +1945,321 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`främmandespråksforskning` (sv)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`läsintryck` (sv)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,78 +2269,78 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,132 +2350,132 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,46 +2512,46 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,83 +2588,83 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,51 +2674,51 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,51 +2728,51 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,46 +2782,46 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`lärsituationer` (sv)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`lärsituation` (sv)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,24 +3047,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3101,24 +3101,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,24 +3155,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,213 +3214,213 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`läsförkunskaper` (sv)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3565,530 +3565,152 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`läsförkunskaper` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`läsmiljöns` (sv)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>`verbalspråket` (sv)</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DF</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>`högstadie` (sv)</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>GSV3FP</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>`framåtsiktande` (sv)</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>ATY2B8</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>`additon` (en)</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>ATY2B8</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>`schlarly` (en)</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>GTY2N5</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>`samhällssyttringar` (sv)</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J5</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>`tilllämpa` (sv)</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>`creits` (en)</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>`brign` (en)</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>`othe` (en)</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>`rmedia` (en)</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E135"/>
+  <autoFilter ref="A1:E121"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4330,34 +3952,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,29 +482,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,98 +514,3257 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>AR2009</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`stilistic` (en)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AR2010</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`inlämmningsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AR2012</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`accademic` (en)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GAR39K</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`htat` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GAR39L</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`selction` (en)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AEN252</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`criticially` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AEN252</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`oligatory` (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AEN25S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`ttheir` (en)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`froming` (en)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BZ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`ochspanskspråkiga` (sv)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EN2028</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`analye` (en)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EN2043</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`knowlege` (en)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>EN2046</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`ämnesdidaktiskområde` (sv)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>EN3063</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`coomprising` (en)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EN3071</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`samtidafrågor` (sv)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GEN33R</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`förseminarieupgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`beteen` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`devlopment` (en)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GEN3BQ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`intepreted` (en)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`bedöming` (sv)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`föväntas` (sv)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`ideströmningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`literarature` (en)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DJ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`anlyses` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`anlyses` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`indepently` (en)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`knowlege` (en)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`literarature` (en)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AFR29D</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`franskpråkig` (sv)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`percieving` (en)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GFR2A8</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GFR2HZ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`orbally` (en)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`defens` (en)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`ehtics` (en)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`godänd` (sv)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`ehtics` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`teachning` (en)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`godänd` (sv)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GIT2A3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`indentify` (en)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GIT2AE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`particicpation` (en)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TH</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`contextualise` (en)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`themself` (en)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GIT2Y8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`nlämningsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GJP23S</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`språkfärdiget` (sv)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GJP2MZ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`opprtunity` (en)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GJP37U</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`sritten` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GJP37W</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`featuers` (en)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GJP39V</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`utanförperspektiv` (sv)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>JP1045</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`gundläggande` (sv)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GKI2PY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`forsätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CB</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>KI1030</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>KI1043</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>KI1051</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`textsabout` (en)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
           <t>GPR2W2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GN</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`tha` (en)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>PR2003</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`thsi` (en)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>PR2004</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`prinicipe` (en)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>PR2005</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`credis` (en)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GRY28U</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`formualte` (en)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`assessement` (en)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`obilgatory` (en)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GRY2LE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`sccholarly` (en)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GRY38S</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`läsförståesle` (sv)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GSP2KS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`förtjänstersåväl` (sv)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`ställdakrav` (sv)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>`tidsramargenomföra` (sv)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`vilarpå` (sv)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SP1050</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`assigments` (en)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`realtion` (en)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`semantical` (en)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`communciation` (en)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`pracitse` (en)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`jämörs` (sv)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GSS39U</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`ochförhållningssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BH</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>`writtem` (en)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`framställing` (sv)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>`refelction` (en)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>`tillfredställande` (sv)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`witten` (en)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>`näbaserade` (sv)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`änvänder` (sv)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`inlärartal` (sv)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`affrican` (en)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`centrual` (en)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`dealrs` (en)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`dourse` (en)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`egarding` (en)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`prespectives` (en)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`relatec` (en)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`researchj` (en)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`teorritoriality` (en)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`användingen` (sv)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SS3009</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`skriftspråksanvänding` (sv)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`läsförkunskaper` (sv)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`tiilämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`närstudiet` (sv)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`verbalspråket` (sv)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`edcuation` (en)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ATY29E</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`tyskpråkig` (sv)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`additon` (en)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`schlarly` (en)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`samhällssyttringar` (sv)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`tilllämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`creits` (en)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`brign` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>TY3016</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`assingments` (en)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E123"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -617,6 +3776,240 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,29 +482,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,98 +514,3284 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>AR2009</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`stilistic` (en)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AR2010</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`inlämmningsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AR2012</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`accademic` (en)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GAR39K</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`htat` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GAR39L</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`selction` (en)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AEN252</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`criticially` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AEN252</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`oligatory` (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AEN25S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`ttheir` (en)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`froming` (en)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BZ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`ochspanskspråkiga` (sv)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EN2028</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`analye` (en)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EN2043</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`knowlege` (en)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>EN2046</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`ämnesdidaktiskområde` (sv)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>EN3063</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`coomprising` (en)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EN3071</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`samtidafrågor` (sv)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GEN33R</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`förseminarieupgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`beteen` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`devlopment` (en)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GEN3BQ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`intepreted` (en)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`bedöming` (sv)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`föväntas` (sv)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`ideströmningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`literarature` (en)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DJ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`anlyses` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`anlyses` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`indepently` (en)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`knowlege` (en)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`literarature` (en)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AFR29D</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`franskpråkig` (sv)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`percieving` (en)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GFR2A8</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GFR2HZ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`orbally` (en)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`defens` (en)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`ehtics` (en)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`godänd` (sv)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`ehtics` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`teachning` (en)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`godänd` (sv)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GIT2A3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`indentify` (en)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GIT2AE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`particicpation` (en)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TH</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`contextualise` (en)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`themself` (en)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GIT2Y8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`nlämningsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GJP23S</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`språkfärdiget` (sv)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GJP2MZ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`opprtunity` (en)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GJP37U</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`sritten` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GJP37W</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`featuers` (en)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GJP39V</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`utanförperspektiv` (sv)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>JP1045</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`gundläggande` (sv)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GKI2PY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`forsätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CB</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>KI1030</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>KI1043</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>KI1051</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`textsabout` (en)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
           <t>GPR2W2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GN</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`tha` (en)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>PR2003</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`thsi` (en)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>PR2004</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`prinicipe` (en)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>PR2005</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`credis` (en)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GRY28U</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`formualte` (en)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`assessement` (en)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`obilgatory` (en)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GRY2LE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`sccholarly` (en)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GRY38S</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`läsförståesle` (sv)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GSP2KS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`förtjänstersåväl` (sv)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`ställdakrav` (sv)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>`tidsramargenomföra` (sv)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`vilarpå` (sv)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SP1050</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`assigments` (en)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`realtion` (en)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`semantical` (en)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`communciation` (en)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`pracitse` (en)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`jämörs` (sv)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GSS39U</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`ochförhållningssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BH</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>`writtem` (en)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`framställing` (sv)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>`refelction` (en)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>`tillfredställande` (sv)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`witten` (en)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>`näbaserade` (sv)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`änvänder` (sv)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`inlärartal` (sv)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`affrican` (en)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`centrual` (en)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`dealrs` (en)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`dourse` (en)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`egarding` (en)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`prespectives` (en)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`relatec` (en)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`researchj` (en)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`teorritoriality` (en)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`användingen` (sv)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SS3009</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`skriftspråksanvänding` (sv)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`läsförkunskaper` (sv)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`tiilämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`närstudiet` (sv)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`verbalspråket` (sv)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`edcuation` (en)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ATY29E</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`tyskpråkig` (sv)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`additon` (en)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`schlarly` (en)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`samhällssyttringar` (sv)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`tilllämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`creits` (en)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`brign` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>TY3016</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`assingments` (en)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>HAFSA</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>`västafrika` (sv)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E124"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -617,6 +3803,242 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3763,35 +3763,8 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>HAFSA</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>`västafrika` (sv)</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E124"/>
+  <autoFilter ref="A1:E123"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4037,8 +4010,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`the` — …resentations of varying length.  \### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3763,35 +3763,8 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>HAFSA</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>`västafrika` (sv)</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E124"/>
+  <autoFilter ref="A1:E123"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4037,8 +4010,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1687,7 +1687,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIT2TH</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`contextualise` (en)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,29 +1724,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,24 +1940,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,51 +2021,51 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,51 +2291,51 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,17 +2345,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,24 +3155,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`läsförkunskaper` (sv)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`läsförkunskaper` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`edcuation` (en)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -3415,34 +3415,34 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`edcuation` (en)</t>
+          <t>`tyskpråkig` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`tyskpråkig` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3538,19 +3538,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`samhällssyttringar` (sv)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`tilllämpa` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3614,24 +3614,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`creits` (en)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`brign` (en)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`othe` (en)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3727,44 +3727,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`rmedia` (en)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E123"/>
+  <autoFilter ref="A1:E122"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4008,8 +3981,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -604,35 +604,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>HAFSA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>`västafrika` (sv)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E7"/>
+  <autoFilter ref="A1:E6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -644,8 +617,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,29 +482,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,98 +514,3230 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`the` — …resentations of varying length.  \### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>AR2009</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`stilistic` (en)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AR2010</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`inlämmningsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AR2012</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`accademic` (en)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GAR39K</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`htat` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GAR39L</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ARA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`selction` (en)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AEN252</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`criticially` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AEN252</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`oligatory` (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AEN25S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`ttheir` (en)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`froming` (en)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AEN2BZ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`ochspanskspråkiga` (sv)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EN2028</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`analye` (en)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EN2043</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`knowlege` (en)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>EN2046</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`ämnesdidaktiskområde` (sv)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>EN3063</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`coomprising` (en)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EN3071</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`samtidafrågor` (sv)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GEN33R</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`förseminarieupgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`beteen` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`devlopment` (en)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GEN3BQ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`intepreted` (en)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`bedöming` (sv)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`föväntas` (sv)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`ideströmningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`literarature` (en)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DJ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`anlyses` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`anlyses` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`indepently` (en)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`knowlege` (en)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`literarature` (en)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AFR29D</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`franskpråkig` (sv)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`percieving` (en)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GFR2A8</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GFR2HZ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`orbally` (en)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`defens` (en)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`ehtics` (en)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`godänd` (sv)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`ehtics` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`teachning` (en)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`godänd` (sv)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GIT2A3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`indentify` (en)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GIT2AE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`particicpation` (en)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GIT2TK</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`themself` (en)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GIT2Y8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`nlämningsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GJP23S</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`språkfärdiget` (sv)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GJP2MZ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`opprtunity` (en)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GJP37U</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`sritten` (en)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GJP37W</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`featuers` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GJP39V</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`utanförperspektiv` (sv)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>JP1045</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JAA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`gundläggande` (sv)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GKI2PY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`forsätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>KI1030</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>KI1043</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>KI1051</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`textsabout` (en)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>GPR2W2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>PRA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>`tha` (en)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>PR2003</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`thsi` (en)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>PR2004</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`prinicipe` (en)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>PR2005</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`credis` (en)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GRY28U</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`formualte` (en)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`assessement` (en)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GRY2B4</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`obilgatory` (en)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GRY2LE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`sccholarly` (en)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GRY38S</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`läsförståesle` (sv)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GSP2KS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`förtjänstersåväl` (sv)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`ställdakrav` (sv)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`tidsramargenomföra` (sv)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>`vilarpå` (sv)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GSP3GW</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`theseis` (en)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SP1050</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`assigments` (en)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`realtion` (en)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`semantical` (en)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SP2024</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`communciation` (en)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`amd` (en)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`pracitse` (en)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`jämörs` (sv)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GSS39U</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`ochförhållningssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BH</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`writtem` (en)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>`framställing` (sv)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BK</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`refelction` (en)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>`tillfredställande` (sv)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>`witten` (en)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`näbaserade` (sv)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>`änvänder` (sv)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`inlärartal` (sv)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`affrican` (en)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`centrual` (en)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`dealrs` (en)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`dourse` (en)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`egarding` (en)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`prespectives` (en)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`relatec` (en)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`researchj` (en)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`teorritoriality` (en)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`användingen` (sv)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SS3009</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`skriftspråksanvänding` (sv)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`läsförkunskaper` (sv)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`tiilämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`närstudiet` (sv)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`verbalspråket` (sv)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`edcuation` (en)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ATY29E</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`tyskpråkig` (sv)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`additon` (en)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`schlarly` (en)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`samhällssyttringar` (sv)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`tilllämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`creits` (en)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`brign` (en)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>TY3016</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`assingments` (en)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E122"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -617,6 +3749,238 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  \### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3736,8 +3736,35 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>HAFSA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`västafrika` (sv)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E122"/>
+  <autoFilter ref="A1:E123"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3981,6 +4008,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`the` — …resentations of varying length.  \### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3736,35 +3736,8 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>HAFSA</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>`västafrika` (sv)</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E123"/>
+  <autoFilter ref="A1:E122"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4008,8 +3981,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>`proficiencythrough` (en)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
@@ -509,15 +531,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2011-11-29</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -536,15 +568,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>`assesment` (en)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -563,15 +605,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>`diffrent` (en)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -590,15 +642,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>`stilistic` (en)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
@@ -617,15 +679,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
@@ -644,15 +716,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>`accademic` (en)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
@@ -671,15 +749,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>`htat` (en)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
@@ -698,15 +782,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>`selction` (en)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
@@ -725,15 +815,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>`criticially` (en)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
@@ -752,15 +848,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>`oligatory` (en)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
@@ -779,15 +881,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>`ttheir` (en)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
@@ -806,15 +914,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>`froming` (en)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
@@ -833,15 +947,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
@@ -860,15 +980,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>`analye` (en)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
@@ -887,15 +1017,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2015-03-16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>`knowlege` (en)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
@@ -914,15 +1050,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
@@ -941,15 +1083,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>`coomprising` (en)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
@@ -968,15 +1120,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
@@ -995,15 +1153,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
@@ -1022,15 +1186,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>`beteen` (en)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
@@ -1049,15 +1219,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>`devlopment` (en)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
@@ -1076,15 +1252,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>`intepreted` (en)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
@@ -1103,15 +1285,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>`bedöming` (sv)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1130,15 +1318,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>`föväntas` (sv)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1157,15 +1351,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>`ideströmningar` (sv)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1184,15 +1384,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>`literarature` (en)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
@@ -1211,15 +1417,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>`anlyses` (en)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
@@ -1238,15 +1450,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>`anlyses` (en)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1265,15 +1483,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>`indepently` (en)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1292,15 +1516,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>`knowlege` (en)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1319,15 +1549,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>`literarature` (en)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
@@ -1346,15 +1582,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>`franskpråkig` (sv)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
@@ -1373,15 +1619,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>`amd` (en)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
@@ -1400,15 +1652,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>`percieving` (en)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
@@ -1427,15 +1685,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
@@ -1454,15 +1718,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>`orbally` (en)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
@@ -1481,15 +1751,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>`defens` (en)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
@@ -1508,15 +1784,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>`ehtics` (en)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
@@ -1535,15 +1817,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>`godänd` (sv)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
@@ -1562,15 +1850,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>`ehtics` (en)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
@@ -1589,15 +1883,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>`teachning` (en)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
@@ -1616,15 +1916,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>`godänd` (sv)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
@@ -1643,15 +1949,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>`indentify` (en)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
@@ -1670,15 +1986,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>`particicpation` (en)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
@@ -1697,15 +2023,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>`themself` (en)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
@@ -1724,15 +2060,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
@@ -1751,15 +2097,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
@@ -1778,15 +2130,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>`opprtunity` (en)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
@@ -1805,15 +2163,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>`sritten` (en)</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
@@ -1832,15 +2196,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>`featuers` (en)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
@@ -1859,15 +2229,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
@@ -1886,15 +2262,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>2013-10-31</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>`gundläggande` (sv)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
@@ -1913,15 +2295,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>`forsätter` (sv)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
@@ -1940,15 +2328,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
@@ -1967,15 +2361,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
@@ -1994,15 +2398,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>`literära` (sv)</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
@@ -2021,15 +2431,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>`textsabout` (en)</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
@@ -2048,15 +2464,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>2022-04-26</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
@@ -2075,15 +2497,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>`tha` (en)</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
@@ -2102,15 +2530,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>`thsi` (en)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
@@ -2129,15 +2567,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>`prinicipe` (en)</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
@@ -2156,15 +2604,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>`credis` (en)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
@@ -2183,15 +2641,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2019-03-25</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>`formualte` (en)</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
@@ -2210,15 +2674,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>`assessement` (en)</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
@@ -2237,15 +2707,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>`obilgatory` (en)</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
@@ -2264,15 +2740,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2020-12-28</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>`sccholarly` (en)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
@@ -2291,15 +2773,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>`läsförståesle` (sv)</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
@@ -2318,15 +2806,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2020-11-20</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>`theseis` (en)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
@@ -2345,15 +2839,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -2372,15 +2872,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>`ställdakrav` (sv)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -2399,15 +2905,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -2426,15 +2938,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>`vilarpå` (sv)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -2453,15 +2971,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>`theseis` (en)</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -2480,15 +3004,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>`assigments` (en)</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
@@ -2507,15 +3037,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>`realtion` (en)</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
@@ -2534,15 +3070,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>`semantical` (en)</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
@@ -2561,15 +3103,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>`communciation` (en)</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
@@ -2588,15 +3136,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>`amd` (en)</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
@@ -2615,15 +3169,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>`pracitse` (en)</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
@@ -2642,15 +3202,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>`jämörs` (sv)</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
@@ -2669,15 +3235,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
@@ -2696,15 +3268,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>`writtem` (en)</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
@@ -2723,15 +3301,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>`framställing` (sv)</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
@@ -2750,15 +3334,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>`refelction` (en)</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
@@ -2777,15 +3367,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>`tillfredställande` (sv)</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
@@ -2804,15 +3400,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>`witten` (en)</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
@@ -2831,15 +3433,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>`näbaserade` (sv)</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
@@ -2858,15 +3466,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>`änvänder` (sv)</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
@@ -2885,15 +3499,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>`inlärartal` (sv)</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -2912,15 +3532,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>`affrican` (en)</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -2939,15 +3565,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>`centrual` (en)</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -2966,15 +3598,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>`dealrs` (en)</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -2993,15 +3631,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>`dourse` (en)</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3020,15 +3664,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>`egarding` (en)</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3047,15 +3697,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>`prespectives` (en)</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3074,15 +3730,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>`relatec` (en)</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3101,15 +3763,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>`researchj` (en)</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3128,15 +3796,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>`teorritoriality` (en)</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3155,15 +3829,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>`användingen` (sv)</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
@@ -3182,15 +3862,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
@@ -3209,15 +3895,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
@@ -3236,15 +3928,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>`läsförkunskaper` (sv)</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
@@ -3263,15 +3961,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
@@ -3290,15 +3994,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>`tiilämpa` (sv)</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
@@ -3317,15 +4027,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>`närstudiet` (sv)</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
@@ -3344,15 +4060,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>`verbalspråket` (sv)</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
@@ -3371,15 +4093,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
@@ -3398,15 +4126,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>`edcuation` (en)</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
@@ -3425,15 +4159,25 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>`tyskpråkig` (sv)</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
@@ -3452,15 +4196,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>`additon` (en)</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -3479,15 +4229,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>`schlarly` (en)</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -3506,15 +4262,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>`sjävständighet` (sv)</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
@@ -3533,15 +4295,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
@@ -3560,15 +4328,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>`tilllämpa` (sv)</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
@@ -3587,15 +4361,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>Felstavning</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>`sjävständighet` (sv)</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
@@ -3614,15 +4394,25 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>`creits` (en)</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
@@ -3641,15 +4431,25 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>`brign` (en)</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
@@ -3668,15 +4468,25 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>`othe` (en)</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
@@ -3695,15 +4505,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>`rmedia` (en)</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
@@ -3722,265 +4542,275 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2014-01-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>`assingments` (en)</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E122"/>
+  <autoFilter ref="A1:G122"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>AR1018</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,34 +494,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
+          <t>2012-04-19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2017-10-03</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`proficiencythrough` (en)</t>
+          <t>`språkfärdighe` (sv)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,27 +531,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`assesment` (en)</t>
+          <t>`the` — …esentations of varying length.  \### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`diffrent` (en)</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2017-10-03</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -657,19 +657,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`stilistic` (en)</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -689,24 +689,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`inlämmningsuppgifter` (sv)</t>
+          <t>`stilistic` (en)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AR2012</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -716,30 +716,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`accademic` (en)</t>
+          <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +753,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -760,19 +764,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`htat` (en)</t>
+          <t>`accademic` (en)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -782,40 +786,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`selction` (en)</t>
+          <t>`möj` (sv)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>GAR39K</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -826,29 +830,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`criticially` (en)</t>
+          <t>`htat` (en)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>GAR39L</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -859,19 +863,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`oligatory` (en)</t>
+          <t>`selction` (en)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,7 +885,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -892,19 +896,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`ttheir` (en)</t>
+          <t>`criticially` (en)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -914,7 +918,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -925,19 +929,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`froming` (en)</t>
+          <t>`oligatory` (en)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -947,30 +951,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`ochspanskspråkiga` (sv)</t>
+          <t>`ttheir` (en)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -980,34 +984,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`analye` (en)</t>
+          <t>`frå` (sv)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1028,19 +1028,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`froming` (en)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1061,19 +1061,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`ämnesdidaktiskområde` (sv)</t>
+          <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2013-11-14</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1098,19 +1098,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`coomprising` (en)</t>
+          <t>`analye` (en)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1120,30 +1120,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2015-03-16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`samtidafrågor` (sv)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2023-03-03</t>
+          <t>2016-02-05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1164,19 +1164,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,10 +1186,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>2013-11-14</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -1197,19 +1201,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`coomprising` (en)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1219,30 +1223,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2015-03-12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,30 +1256,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2015-03-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`ämneslärarexame` (sv)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>EN3074</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1296,19 +1300,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`sät` (sv)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,7 +1322,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1329,19 +1333,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`tilläm` (sv)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1351,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2018-03-22</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1362,19 +1366,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`föror` (sv)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN28Q</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1384,30 +1388,34 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>2019-03-21</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`inlämnin` (sv)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1417,30 +1425,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1450,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1461,19 +1469,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1483,7 +1491,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1494,19 +1502,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1516,7 +1524,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1527,19 +1535,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1549,47 +1557,43 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Felstavning</t>
@@ -1597,128 +1601,128 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`franskpråkig` (sv)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`språku` (sv)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1729,29 +1733,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`orbally` (en)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1762,29 +1766,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1795,62 +1799,62 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1861,19 +1865,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1883,30 +1887,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`teachning` (en)</t>
+          <t>`franskpråkig` (sv)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1916,47 +1924,43 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -1964,140 +1968,128 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`litterä` (sv)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2108,95 +2100,95 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`språku` (sv)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`språkundervisnin` (sv)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`språklär` (sv)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2207,62 +2199,62 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2273,29 +2265,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2306,99 +2298,95 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`franskspråki` (sv)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GFR3HK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2409,98 +2397,106 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`språklär` (sv)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>2019-08-23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2508,71 +2504,71 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GIT2TD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2012-10-31</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`föruts` (sv)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2582,330 +2578,338 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GIT2TN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`föruts` (sv)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GIT2YE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`skönlitter` (sv)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`bedö` (sv)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GJP2N2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`bedö` (sv)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2916,29 +2920,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2013-10-31</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2949,227 +2953,231 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`förbere` (sv)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`språku` (sv)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3180,29 +3188,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GPR256</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3213,62 +3221,62 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`språ` (sv)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3279,32 +3287,36 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>PR1024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>Felstavning</t>
@@ -3312,32 +3324,36 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`översättni` (sv)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1024</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3345,65 +3361,73 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3411,128 +3435,128 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -3543,95 +3567,95 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`språkundervisn` (sv)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3642,359 +3666,359 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSP2W6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`språklär` (sv)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>`läsförkunskaper` (sv)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -4005,95 +4029,95 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`inlämnin` (sv)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -4104,132 +4128,128 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>`edcuation` (en)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>`tyskpråkig` (sv)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -4240,29 +4260,29 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -4273,62 +4293,62 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>`samhällssyttringar` (sv)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -4339,29 +4359,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>`tilllämpa` (sv)</t>
+          <t>`därutöve` (sv)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -4372,147 +4392,131 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`föror` (sv)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>`creits` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>`brign` (en)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>`othe` (en)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -4520,54 +4524,1538 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>`rmedia` (en)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>`centrual` (en)</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>`dealrs` (en)</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>`dourse` (en)</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>`egarding` (en)</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>`prespectives` (en)</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>`relatec` (en)</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>`researchj` (en)</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>`teorritoriality` (en)</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>SS3002</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>`fördju` (sv)</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>SS3004</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>`självständ` (sv)</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>`användingen` (sv)</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>SS3009</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>`skriftspråksanvänding` (sv)</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>`läsförkunskape` (sv)</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>`läsförkunskaper` (sv)</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>`läsu` (sv)</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZU</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>`språkut` (sv)</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZV</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>`språ` (sv)</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZV</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>`språkut` (sv)</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>`grundläggand` (sv)</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>`grundläggand` (sv)</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>`tiilämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>`närstudiet` (sv)</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>`verbalspråket` (sv)</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>`framåtsiktande` (sv)</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>`edcuation` (en)</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>ATY29E</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>`tyskpråkig` (sv)</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>`additon` (en)</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>`schlarly` (en)</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CT</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>`språkun` (sv)</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>`samhällssyttringar` (sv)</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>`språkun` (sv)</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J5</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>`tilllämpa` (sv)</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J9</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>`språkun` (sv)</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>`sjävständighet` (sv)</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>TY1038</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2011-10-10</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>`ämneslärar` (sv)</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>`förf` (sv)</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>`creits` (en)</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>`brign` (en)</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>`säkerhe` (sv)</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>TY3016</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2014-01-27</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>`assingments` (en)</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G122"/>
+  <autoFilter ref="A1:G166"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -4811,6 +6299,94 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId330"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AR1018</t>
+          <t>AR1025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,34 +494,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2012-04-19</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`språkfärdighe` (sv)</t>
+          <t>`proficiencythrough` (en)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AR1025</t>
+          <t>AR2001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,27 +531,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
+          <t>2011-11-29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2017-10-03</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`proficiencythrough` (en)</t>
+          <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`the` — …esentations of varying length.  \### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
+          <t>`assesment` (en)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`assesment` (en)</t>
+          <t>`diffrent` (en)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AR2001</t>
+          <t>AR2009</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2011-11-29</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2017-10-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -657,19 +657,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`diffrent` (en)</t>
+          <t>`stilistic` (en)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AR2009</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -689,24 +689,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`stilistic` (en)</t>
+          <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AR2010</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -716,34 +716,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2015-09-15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2017-10-03</t>
-        </is>
-      </c>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`inlämmningsuppgifter` (sv)</t>
+          <t>`accademic` (en)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AR2012</t>
+          <t>GAR39K</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -753,7 +749,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2017-09-13</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -764,19 +760,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`accademic` (en)</t>
+          <t>`htat` (en)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>GAR39L</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -786,40 +782,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`möj` (sv)</t>
+          <t>`selction` (en)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GAR39K</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -830,29 +826,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`htat` (en)</t>
+          <t>`criticially` (en)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GAR39L</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -863,19 +859,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`selction` (en)</t>
+          <t>`oligatory` (en)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -896,19 +892,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`criticially` (en)</t>
+          <t>`ttheir` (en)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -918,7 +914,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -929,19 +925,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`oligatory` (en)</t>
+          <t>`froming` (en)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,30 +947,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`ttheir` (en)</t>
+          <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -984,30 +980,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`frå` (sv)</t>
+          <t>`analye` (en)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2015-03-16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1028,19 +1028,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`froming` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2016-02-05</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1061,19 +1061,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`ochspanskspråkiga` (sv)</t>
+          <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1098,19 +1098,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`analye` (en)</t>
+          <t>`coomprising` (en)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1120,30 +1120,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
+          <t>2015-03-12</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1164,19 +1164,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`ämnesdidaktiskområde` (sv)</t>
+          <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,14 +1186,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2013-11-14</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -1201,19 +1197,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`coomprising` (en)</t>
+          <t>`beteen` (en)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1223,30 +1219,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`samtidafrågor` (sv)</t>
+          <t>`devlopment` (en)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,30 +1252,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`ämneslärarexame` (sv)</t>
+          <t>`intepreted` (en)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>EN3074</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1289,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1300,19 +1296,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`sät` (sv)</t>
+          <t>`bedöming` (sv)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1333,19 +1329,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`tilläm` (sv)</t>
+          <t>`föväntas` (sv)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1351,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1366,19 +1362,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`föror` (sv)</t>
+          <t>`ideströmningar` (sv)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GEN28Q</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,34 +1384,30 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2019-03-21</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`inlämnin` (sv)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN3DJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,30 +1417,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2023-03-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`förseminarieupgifter` (sv)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1450,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1469,19 +1461,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`beteen` (en)</t>
+          <t>`anlyses` (en)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1491,7 +1483,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1502,19 +1494,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`devlopment` (en)</t>
+          <t>`indepently` (en)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1524,7 +1516,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1535,19 +1527,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`intepreted` (en)</t>
+          <t>`knowlege` (en)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1557,43 +1549,47 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`bedöming` (sv)</t>
+          <t>`literarature` (en)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Felstavning</t>
@@ -1601,128 +1597,128 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`föväntas` (sv)</t>
+          <t>`franskpråkig` (sv)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`ideströmningar` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`språku` (sv)</t>
+          <t>`percieving` (en)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GEN3DJ</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1733,29 +1729,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`orbally` (en)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1766,29 +1762,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`anlyses` (en)</t>
+          <t>`defens` (en)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1799,62 +1795,62 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>`indepently` (en)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`knowlege` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1865,19 +1861,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`literarature` (en)</t>
+          <t>`ehtics` (en)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1887,34 +1883,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`franskpråkig` (sv)</t>
+          <t>`teachning` (en)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1924,43 +1916,47 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`godänd` (sv)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>GIT2A3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -1968,128 +1964,140 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>`percieving` (en)</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>GIT2AE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>2019-08-23</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>`litterä` (sv)</t>
+          <t>`particicpation` (en)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
+          <t>`themself` (en)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>`orbally` (en)</t>
+          <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2100,95 +2108,95 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>`språku` (sv)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>`språkundervisnin` (sv)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>`språklär` (sv)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2199,62 +2207,62 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>`defens` (en)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2013-10-31</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2265,29 +2273,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2298,95 +2306,99 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`franskspråki` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`ehtics` (en)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>`teachning` (en)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GFR3HK</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2397,106 +2409,98 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`språklär` (sv)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`godänd` (sv)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIT2A3</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2022-04-26</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIT2AE</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2504,71 +2508,71 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`particicpation` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIT2TD</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`föruts` (sv)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2578,338 +2582,330 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`themself` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GIT2TN</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`föruts` (sv)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2019-03-25</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`nlämningsuppgifter` (sv)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GIT2YE</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2019-09-11</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`skönlitter` (sv)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`bedö` (sv)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GJP2N2</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`bedö` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2920,29 +2916,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2953,231 +2949,227 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`förbere` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`språku` (sv)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3188,29 +3180,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GPR256</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2018-10-10</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3221,62 +3213,62 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`språ` (sv)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3287,36 +3279,32 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>PR1024</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Felstavning</t>
@@ -3324,36 +3312,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>`översättni` (sv)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2012-10-31</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3361,73 +3345,65 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3435,128 +3411,128 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -3567,95 +3543,95 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>`språkundervisn` (sv)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3666,359 +3642,359 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSP2W6</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>`språklär` (sv)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`läsförkunskaper` (sv)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -4029,95 +4005,95 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>`inlämnin` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -4128,128 +4104,132 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`framåtsiktande` (sv)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`edcuation` (en)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`tyskpråkig` (sv)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -4260,29 +4240,29 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -4293,62 +4273,62 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -4359,29 +4339,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>`därutöve` (sv)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -4392,131 +4372,147 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>`föror` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -4524,32 +4520,36 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>2014-01-27</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -4557,1505 +4557,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>SS2009</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>`dealrs` (en)</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>SS2009</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>`dourse` (en)</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>SS2009</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>`egarding` (en)</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>SS2009</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>`prespectives` (en)</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>SS2009</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>`relatec` (en)</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>SS2009</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>`researchj` (en)</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>SS2009</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>`teorritoriality` (en)</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>SS3002</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2014-03-20</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>`fördju` (sv)</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>SS3004</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2014-04-11</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>`självständ` (sv)</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>SS3007</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>`användingen` (sv)</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>SS3009</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>`skriftspråksanvänding` (sv)</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CP</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>`framåtsiktande` (sv)</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CP</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>`läsförkunskape` (sv)</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CP</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>`läsförkunskaper` (sv)</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CQ</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>`framåtsiktande` (sv)</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>ASV2CQ</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>`läsu` (sv)</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZU</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>`språkut` (sv)</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZV</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>`språ` (sv)</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZV</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>`språkut` (sv)</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZW</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>`grundläggand` (sv)</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZX</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>`grundläggand` (sv)</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>GSV2ZX</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>`tiilämpa` (sv)</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>`närstudiet` (sv)</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>GSV3DE</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>`verbalspråket` (sv)</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>GSV3FP</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>`framåtsiktande` (sv)</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>GSV3FP</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>SVE</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>`edcuation` (en)</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>ATY29E</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>`tyskpråkig` (sv)</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>ATY2B8</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>`additon` (en)</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>ATY2B8</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>`schlarly` (en)</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>GTY2N5</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CT</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>`språkun` (sv)</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>`samhällssyttringar` (sv)</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>GTY3CU</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>`språkun` (sv)</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J5</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>`tilllämpa` (sv)</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>`språkun` (sv)</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>TY1038</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2011-10-10</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>`ämneslärar` (sv)</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>TY2007</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>`förf` (sv)</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>`creits` (en)</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>`brign` (en)</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>`othe` (en)</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>`rmedia` (en)</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2014-01-27</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>`säkerhe` (sv)</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2014-01-27</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G166"/>
+  <autoFilter ref="A1:G122"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -6299,94 +4811,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId330"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2087,50 +2087,50 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GIT3KP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`indentify` (en)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KP</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GIT3KR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2141,19 +2141,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`andcultural` (en)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2163,30 +2163,30 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2207,19 +2207,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2229,30 +2229,30 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2262,40 +2262,40 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GJP39V</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2306,52 +2306,52 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`utanförperspektiv` (sv)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2013-10-31</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2361,34 +2361,30 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2398,30 +2394,30 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2431,73 +2427,77 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2508,19 +2508,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2530,34 +2530,30 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2012-10-31</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2022-04-26</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2567,14 +2563,10 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2582,19 +2574,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2604,7 +2596,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2619,32 +2611,36 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2652,32 +2648,36 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2685,19 +2685,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2718,19 +2718,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2751,19 +2751,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2773,40 +2773,40 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2817,29 +2817,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2850,19 +2850,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3004,30 +3004,30 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3048,19 +3048,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSP3KU</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3081,19 +3081,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSP3KV</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3114,29 +3114,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSP3KV</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3147,29 +3147,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3180,95 +3180,95 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`semantical` (en)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3279,19 +3279,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3301,30 +3301,30 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -3345,19 +3345,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -3378,19 +3378,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3400,30 +3400,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3433,30 +3433,30 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -3477,19 +3477,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3499,30 +3499,30 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3532,30 +3532,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3576,19 +3576,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3598,30 +3598,30 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3631,23 +3631,23 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
@@ -3667,15 +3667,19 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`inlärartal` (sv)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3700,7 +3704,11 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3708,7 +3716,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3733,7 +3741,11 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3741,7 +3753,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -3766,7 +3778,11 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3774,7 +3790,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -3799,7 +3815,11 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3807,7 +3827,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -3819,7 +3839,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3829,30 +3849,34 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3862,139 +3886,155 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>`läsförkunskaper` (sv)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -4005,29 +4045,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -4038,19 +4078,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4060,7 +4100,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -4071,19 +4111,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`läsförkunskaper` (sv)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4093,7 +4133,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -4104,19 +4144,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>`framåtsiktande` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4126,47 +4166,43 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>`edcuation` (en)</t>
+          <t>`närstudiet` (sv)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Felstavning</t>
@@ -4174,29 +4210,29 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>`tyskpråkig` (sv)</t>
+          <t>`verbalspråket` (sv)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -4207,19 +4243,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`edcuation` (en)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4229,30 +4265,34 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`tyskpråkig` (sv)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4262,30 +4302,30 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4301,24 +4341,24 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>`samhällssyttringar` (sv)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4328,7 +4368,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -4339,19 +4379,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>`tilllämpa` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4361,7 +4401,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -4372,19 +4412,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4394,34 +4434,30 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>`creits` (en)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4431,34 +4467,30 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>`brign` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4468,12 +4500,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4483,12 +4515,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>`othe` (en)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4552,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>`rmedia` (en)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4532,42 +4564,116 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>`assingments` (en)</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G122"/>
+  <autoFilter ref="A1:G124"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -4811,6 +4917,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2285,7 +2285,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2013-10-31</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2306,29 +2306,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`utanförperspektiv` (sv)</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2339,19 +2339,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2361,30 +2361,30 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2394,10 +2394,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
@@ -2405,19 +2409,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2427,34 +2431,30 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2464,63 +2464,63 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2530,30 +2530,30 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2563,10 +2563,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2574,19 +2578,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2596,7 +2600,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2012-10-31</t>
+          <t>2013-06-14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2611,19 +2615,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2633,7 +2637,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2648,36 +2652,32 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2019-03-25</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2685,19 +2685,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2784,19 +2784,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2806,63 +2806,63 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSP3KU</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3048,19 +3048,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSP3KU</t>
+          <t>GSP3KV</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3081,19 +3081,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSP3KV</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3114,19 +3114,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSP3KV</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3147,19 +3147,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3180,29 +3180,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3213,29 +3213,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -3246,52 +3246,52 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>`semantical` (en)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3301,30 +3301,30 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -3345,19 +3345,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -3378,19 +3378,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3400,30 +3400,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3439,24 +3439,24 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3472,24 +3472,24 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3499,30 +3499,30 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -3543,19 +3543,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3565,10 +3565,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -3576,19 +3580,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3598,30 +3602,34 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3631,23 +3639,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3686,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>`inlärartal` (sv)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3716,7 +3728,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3753,7 +3765,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -3790,7 +3802,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -3827,7 +3839,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -3864,7 +3876,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -3876,7 +3888,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3886,34 +3898,30 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3923,88 +3931,76 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -4012,32 +4008,36 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`edcuation` (en)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>Felstavning</t>
@@ -4045,95 +4045,95 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`tyskpråkig` (sv)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>`läsförkunskaper` (sv)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -4144,29 +4144,29 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -4177,29 +4177,29 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>`närstudiet` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -4210,52 +4210,52 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>`verbalspråket` (sv)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>`edcuation` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4265,34 +4265,34 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>`tyskpråkig` (sv)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4302,10 +4302,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -4313,19 +4317,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4335,10 +4339,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -4346,19 +4354,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`othe` (en)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>TY3015</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4368,30 +4376,34 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`rmedia` (en)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4401,279 +4413,32 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>2014-01-27</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>`samhällssyttringar` (sv)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J5</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>`tilllämpa` (sv)</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>`sjävständighet` (sv)</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>`creits` (en)</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>`brign` (en)</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>`othe` (en)</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>TY3015</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>`rmedia` (en)</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2014-01-27</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>`assingments` (en)</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G124"/>
+  <autoFilter ref="A1:G117"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -4907,20 +4672,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2087,7 +2087,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIT3KP</t>
+          <t>GIT3KM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2108,19 +2108,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>`indentify` (en)</t>
+          <t>`continuos` (en)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KM</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIT3KR</t>
+          <t>GIT3KN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2141,62 +2141,62 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>`andcultural` (en)</t>
+          <t>`contunuous` (en)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GJP23S</t>
+          <t>GIT3KP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>`språkfärdiget` (sv)</t>
+          <t>`examinationin` (en)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KP</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>GIT3KR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2207,19 +2207,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>`opprtunity` (en)</t>
+          <t>`andcultural` (en)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GJP37U</t>
+          <t>GJP23S</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2229,30 +2229,30 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>`sritten` (en)</t>
+          <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2273,19 +2273,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>`featuers` (en)</t>
+          <t>`opprtunity` (en)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GJP37U</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2295,96 +2295,96 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2013-10-31</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`gundläggande` (sv)</t>
+          <t>`sritten` (en)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`forsätter` (sv)</t>
+          <t>`featuers` (en)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>JP1045</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2013-10-31</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
+          <t>`gundläggande` (sv)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2394,34 +2394,30 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
+          <t>`forsätter` (sv)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KI1043</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2431,30 +2427,30 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KI1051</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2464,73 +2460,77 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`textsabout` (en)</t>
+          <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>KI1043</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>KI1051</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2541,19 +2541,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`textsabout` (en)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2563,34 +2563,30 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2012-10-31</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2022-04-26</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`thsi` (en)</t>
+          <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PR2004</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2600,14 +2596,10 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2615,19 +2607,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`prinicipe` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2637,7 +2629,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2652,32 +2644,36 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`credis` (en)</t>
+          <t>`thsi` (en)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>PR2004</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2685,32 +2681,36 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`formualte` (en)</t>
+          <t>`prinicipe` (en)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>Felstavning (en)</t>
@@ -2718,19 +2718,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`assessement` (en)</t>
+          <t>`credis` (en)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2751,19 +2751,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`obilgatory` (en)</t>
+          <t>`formualte` (en)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2784,19 +2784,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`sccholarly` (en)</t>
+          <t>`assessement` (en)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GRY38S</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2806,40 +2806,40 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`läsförståesle` (sv)</t>
+          <t>`obilgatory` (en)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSP2KS</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2850,29 +2850,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`sccholarly` (en)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GRY38S</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2883,19 +2883,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`förtjänstersåväl` (sv)</t>
+          <t>`läsförståesle` (sv)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSP3GW</t>
+          <t>GSP2KS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2905,23 +2905,23 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`ställdakrav` (sv)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`tidsramargenomföra` (sv)</t>
+          <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`vilarpå` (sv)</t>
+          <t>`ställdakrav` (sv)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`theseis` (en)</t>
+          <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSP3KU</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3037,30 +3037,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`vilarpå` (sv)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSP3KV</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3081,19 +3081,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`theseis` (en)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3114,19 +3114,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`assigments` (en)</t>
+          <t>`fto` (en)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3147,19 +3147,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`realtion` (en)</t>
+          <t>`urther` (en)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3180,29 +3180,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`communciation` (en)</t>
+          <t>`assigments` (en)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3213,29 +3213,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`amd` (en)</t>
+          <t>`realtion` (en)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -3246,19 +3246,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>`pracitse` (en)</t>
+          <t>`communciation` (en)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3268,30 +3268,30 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`jämörs` (sv)</t>
+          <t>`amd` (en)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3301,30 +3301,30 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>`ochförhållningssätt` (sv)</t>
+          <t>`pracitse` (en)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3334,30 +3334,30 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>`writtem` (en)</t>
+          <t>`jämörs` (sv)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -3378,19 +3378,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>`framställing` (sv)</t>
+          <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3411,19 +3411,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>`refelction` (en)</t>
+          <t>`writtem` (en)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3444,19 +3444,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>`tillfredställande` (sv)</t>
+          <t>`framställing` (sv)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3477,19 +3477,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>`witten` (en)</t>
+          <t>`refelction` (en)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3510,19 +3510,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>`näbaserade` (sv)</t>
+          <t>`tillfredställande` (sv)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3532,30 +3532,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>`änvänder` (sv)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3565,34 +3565,30 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>`affrican` (en)</t>
+          <t>`näbaserade` (sv)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3602,27 +3598,23 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>`centrual` (en)</t>
+          <t>`änvänder` (sv)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3646,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>`dealrs` (en)</t>
+          <t>`affrican` (en)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3691,7 +3683,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>`dourse` (en)</t>
+          <t>`centrual` (en)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -3728,7 +3720,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>`egarding` (en)</t>
+          <t>`dealrs` (en)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3765,7 +3757,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>`prespectives` (en)</t>
+          <t>`dourse` (en)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -3802,7 +3794,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>`relatec` (en)</t>
+          <t>`egarding` (en)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -3839,7 +3831,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>`researchj` (en)</t>
+          <t>`prespectives` (en)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -3876,7 +3868,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>`teorritoriality` (en)</t>
+          <t>`relatec` (en)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -3888,7 +3880,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3898,30 +3890,34 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>`användingen` (sv)</t>
+          <t>`researchj` (en)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3931,40 +3927,44 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>`skriftspråksanvänding` (sv)</t>
+          <t>`teorritoriality` (en)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3975,69 +3975,65 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>`tiilämpa` (sv)</t>
+          <t>`användingen` (sv)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>`edcuation` (en)</t>
+          <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Felstavning</t>
@@ -4045,29 +4041,29 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>`tyskpråkig` (sv)</t>
+          <t>`tiilämpa` (sv)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -4078,19 +4074,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>`additon` (en)</t>
+          <t>`edcuation` (en)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4100,30 +4096,34 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>`schlarly` (en)</t>
+          <t>`tyskpråkig` (sv)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4133,30 +4133,30 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`additon` (en)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4172,24 +4172,24 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>`samhällssyttringar` (sv)</t>
+          <t>`schlarly` (en)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -4210,19 +4210,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>`tilllämpa` (sv)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -4243,19 +4243,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>`sjävständighet` (sv)</t>
+          <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4265,34 +4265,30 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>`creits` (en)</t>
+          <t>`tilllämpa` (sv)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4302,34 +4298,30 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>`brign` (en)</t>
+          <t>`sjävständighet` (sv)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4339,12 +4331,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4354,12 +4346,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>`othe` (en)</t>
+          <t>`creits` (en)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4383,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>`rmedia` (en)</t>
+          <t>`brign` (en)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4403,42 +4395,116 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>`othe` (en)</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>`rmedia` (en)</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>`assingments` (en)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G117"/>
+  <autoFilter ref="A1:G119"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -4672,6 +4738,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$H$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -512,7 +518,12 @@
           <t>`proficiencythrough` (en)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>proficiency through</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1025</t>
         </is>
@@ -549,7 +560,8 @@
           <t>`the` — …resentations of varying length.  ### Assessment  Grades for the the _Grammar and Texts_ module are based on continuous assesmen…</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -586,7 +598,12 @@
           <t>`assesment` (en)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>assessment</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -623,7 +640,12 @@
           <t>`diffrent` (en)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>different</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2001</t>
         </is>
@@ -660,7 +682,12 @@
           <t>`stilistic` (en)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>stylistic</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2009</t>
         </is>
@@ -697,7 +724,12 @@
           <t>`inlämmningsuppgifter` (sv)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>inlämningsuppgifter</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
@@ -730,7 +762,12 @@
           <t>`accademic` (en)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>academic</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
@@ -763,7 +800,12 @@
           <t>`htat` (en)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>that</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39K</t>
         </is>
@@ -796,7 +838,12 @@
           <t>`selction` (en)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>selection</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39L</t>
         </is>
@@ -829,7 +876,12 @@
           <t>`criticially` (en)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>critically</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
@@ -862,7 +914,12 @@
           <t>`oligatory` (en)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>obligatory</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
@@ -895,7 +952,12 @@
           <t>`ttheir` (en)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>their</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
@@ -928,7 +990,12 @@
           <t>`froming` (en)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>forming</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
@@ -961,7 +1028,12 @@
           <t>`ochspanskspråkiga` (sv)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>och spanskspråkiga</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
@@ -998,7 +1070,12 @@
           <t>`analye` (en)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>analyse</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
@@ -1031,7 +1108,12 @@
           <t>`knowlege` (en)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>knowledge</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
@@ -1064,7 +1146,12 @@
           <t>`ämnesdidaktiskområde` (sv)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ämnesdidaktiskt område</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
@@ -1101,7 +1188,12 @@
           <t>`coomprising` (en)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>comprising</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
@@ -1134,7 +1226,8 @@
           <t>`samtidafrågor` (sv)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
@@ -1167,7 +1260,12 @@
           <t>`förseminarieupgifter` (sv)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>förseminarieuppgifter</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
@@ -1200,7 +1298,8 @@
           <t>`beteen` (en)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
@@ -1233,7 +1332,12 @@
           <t>`devlopment` (en)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
@@ -1266,7 +1370,12 @@
           <t>`intepreted` (en)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>interpreted</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
@@ -1299,7 +1408,8 @@
           <t>`bedöming` (sv)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1332,7 +1442,12 @@
           <t>`föväntas` (sv)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>förväntas</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1365,7 +1480,12 @@
           <t>`ideströmningar` (sv)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>idéströmningar</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1398,7 +1518,12 @@
           <t>`literarature` (en)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>literature</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
@@ -1431,7 +1556,12 @@
           <t>`anlyses` (en)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DJ</t>
         </is>
@@ -1464,7 +1594,12 @@
           <t>`anlyses` (en)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1497,7 +1632,12 @@
           <t>`indepently` (en)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>independently</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1530,7 +1670,12 @@
           <t>`knowlege` (en)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>knowledge</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1563,7 +1708,12 @@
           <t>`literarature` (en)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>literature</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
@@ -1600,7 +1750,12 @@
           <t>`franskpråkig` (sv)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>franskspråkig</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
@@ -1633,7 +1788,12 @@
           <t>`amd` (en)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
@@ -1666,7 +1826,12 @@
           <t>`percieving` (en)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>perceiving</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
@@ -1699,7 +1864,8 @@
           <t>`writing` — …y basic French grammar in their own text production such as writing writing simple texts or summarizing a newspaper article in good Fre…</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
@@ -1732,7 +1898,12 @@
           <t>`orbally` (en)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>orally</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
@@ -1765,7 +1936,12 @@
           <t>`defens` (en)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>defence</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
@@ -1798,7 +1974,12 @@
           <t>`ehtics` (en)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ethics</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
@@ -1831,7 +2012,12 @@
           <t>`godänd` (sv)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>godkänd</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
@@ -1864,7 +2050,12 @@
           <t>`ehtics` (en)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ethics</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
@@ -1897,7 +2088,12 @@
           <t>`teachning` (en)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>teaching</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
@@ -1930,7 +2126,12 @@
           <t>`godänd` (sv)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>godkänd</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
@@ -1967,7 +2168,12 @@
           <t>`indentify` (en)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>identify</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2A3</t>
         </is>
@@ -2004,7 +2210,12 @@
           <t>`particicpation` (en)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>participation</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2AE</t>
         </is>
@@ -2041,7 +2252,12 @@
           <t>`themself` (en)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>themselves</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
@@ -2078,7 +2294,12 @@
           <t>`nlämningsuppgifter` (sv)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>inlämningsuppgifter</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
@@ -2111,7 +2332,12 @@
           <t>`continuos` (en)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KM</t>
         </is>
@@ -2144,7 +2370,12 @@
           <t>`contunuous` (en)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KN</t>
         </is>
@@ -2177,7 +2408,12 @@
           <t>`examinationin` (en)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>examination in</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KP</t>
         </is>
@@ -2210,7 +2446,12 @@
           <t>`andcultural` (en)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>and cultural</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KR</t>
         </is>
@@ -2243,7 +2484,12 @@
           <t>`språkfärdiget` (sv)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>språkfärdighet</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23S</t>
         </is>
@@ -2276,7 +2522,12 @@
           <t>`opprtunity` (en)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>opportunity</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
@@ -2309,7 +2560,12 @@
           <t>`sritten` (en)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>written</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37U</t>
         </is>
@@ -2342,7 +2598,12 @@
           <t>`featuers` (en)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>features</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
@@ -2375,7 +2636,12 @@
           <t>`gundläggande` (sv)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>grundläggande</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
         </is>
@@ -2408,7 +2674,12 @@
           <t>`forsätter` (sv)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>fortsätter</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
@@ -2441,7 +2712,8 @@
           <t>`and` — …cate unhindered in Chinese on a variety of topics    - read and and understand short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
@@ -2478,7 +2750,8 @@
           <t>`and` — …s such as education, sports, and environment etc.    - read and and comprehend short authentic Chinese texts    - compose short…</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
@@ -2511,7 +2784,12 @@
           <t>`literära` (sv)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>litterära</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1043</t>
         </is>
@@ -2544,7 +2822,12 @@
           <t>`textsabout` (en)</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>texts about</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1051</t>
         </is>
@@ -2577,7 +2860,8 @@
           <t>`languages` — …cific context and to analyse the dynamics between different languages languages and linguistic varieties from a societal perspective. In th…</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
@@ -2610,7 +2894,12 @@
           <t>`tha` (en)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>that</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
@@ -2647,7 +2936,12 @@
           <t>`thsi` (en)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>this</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
@@ -2684,7 +2978,12 @@
           <t>`prinicipe` (en)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>principle</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2004</t>
         </is>
@@ -2721,7 +3020,12 @@
           <t>`credis` (en)</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>credits</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
@@ -2754,7 +3058,12 @@
           <t>`formualte` (en)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>formulate</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
@@ -2787,7 +3096,12 @@
           <t>`assessement` (en)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>assessment</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
@@ -2820,7 +3134,12 @@
           <t>`obilgatory` (en)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>obligatory</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
@@ -2853,7 +3172,12 @@
           <t>`sccholarly` (en)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>scholarly</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
@@ -2886,7 +3210,12 @@
           <t>`läsförståesle` (sv)</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>läsförståelse</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY38S</t>
         </is>
@@ -2919,7 +3248,12 @@
           <t>`theseis` (en)</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>thesis</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2KS</t>
         </is>
@@ -2952,7 +3286,12 @@
           <t>`förtjänstersåväl` (sv)</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>förtjänster såväl</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -2985,7 +3324,12 @@
           <t>`ställdakrav` (sv)</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ställda krav</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -3018,7 +3362,12 @@
           <t>`tidsramargenomföra` (sv)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>tidsramar genomföra</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -3051,7 +3400,12 @@
           <t>`vilarpå` (sv)</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>vilar på</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -3084,7 +3438,12 @@
           <t>`theseis` (en)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>thesis</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
@@ -3117,7 +3476,12 @@
           <t>`fto` (en)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
@@ -3150,7 +3514,12 @@
           <t>`urther` (en)</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>further</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
@@ -3183,7 +3552,12 @@
           <t>`assigments` (en)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>assignments</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
@@ -3216,7 +3590,12 @@
           <t>`realtion` (en)</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>relation</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
@@ -3249,7 +3628,12 @@
           <t>`communciation` (en)</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
@@ -3282,7 +3666,12 @@
           <t>`amd` (en)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
@@ -3315,7 +3704,12 @@
           <t>`pracitse` (en)</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>practise</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
@@ -3348,7 +3742,12 @@
           <t>`jämörs` (sv)</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>jämförs</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
@@ -3381,7 +3780,12 @@
           <t>`ochförhållningssätt` (sv)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>och förhållningssätt</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
@@ -3414,7 +3818,12 @@
           <t>`writtem` (en)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>written</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
@@ -3447,7 +3856,12 @@
           <t>`framställing` (sv)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>framställning</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
@@ -3480,7 +3894,12 @@
           <t>`refelction` (en)</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>reflection</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
@@ -3513,7 +3932,12 @@
           <t>`tillfredställande` (sv)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>tillfredsställande</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
@@ -3546,7 +3970,12 @@
           <t>`witten` (en)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>written</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
@@ -3579,7 +4008,12 @@
           <t>`näbaserade` (sv)</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>nätbaserade</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
@@ -3612,7 +4046,12 @@
           <t>`änvänder` (sv)</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>använder</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
@@ -3649,7 +4088,12 @@
           <t>`affrican` (en)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>African</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3686,7 +4130,12 @@
           <t>`centrual` (en)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>central</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3723,7 +4172,12 @@
           <t>`dealrs` (en)</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>deals</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3760,7 +4214,12 @@
           <t>`dourse` (en)</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>course</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3797,7 +4256,12 @@
           <t>`egarding` (en)</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>regarding</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3834,7 +4298,12 @@
           <t>`prespectives` (en)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>perspectives</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3871,7 +4340,12 @@
           <t>`relatec` (en)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3908,7 +4382,12 @@
           <t>`researchj` (en)</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3945,7 +4424,12 @@
           <t>`teorritoriality` (en)</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>territoriality</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3978,7 +4462,12 @@
           <t>`användingen` (sv)</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>användningen</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
@@ -4011,7 +4500,12 @@
           <t>`skriftspråksanvänding` (sv)</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>skriftspråksanvändning</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
@@ -4044,7 +4538,12 @@
           <t>`tiilämpa` (sv)</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>tillämpa</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
@@ -4077,7 +4576,12 @@
           <t>`edcuation` (en)</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
@@ -4114,7 +4618,12 @@
           <t>`tyskpråkig` (sv)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>tyskspråkig</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
@@ -4147,7 +4656,12 @@
           <t>`additon` (en)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>addition</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -4180,7 +4694,12 @@
           <t>`schlarly` (en)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>scholarly</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -4213,7 +4732,12 @@
           <t>`sjävständighet` (sv)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>självständighet</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
@@ -4246,7 +4770,12 @@
           <t>`samhällssyttringar` (sv)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>samhällsyttringar</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
@@ -4279,7 +4808,12 @@
           <t>`tilllämpa` (sv)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>tillämpa</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
@@ -4312,7 +4846,12 @@
           <t>`sjävständighet` (sv)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>självständighet</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
@@ -4349,7 +4888,12 @@
           <t>`creits` (en)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>credits</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
@@ -4386,7 +4930,8 @@
           <t>`brign` (en)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
@@ -4423,7 +4968,12 @@
           <t>`othe` (en)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
@@ -4460,7 +5010,12 @@
           <t>`rmedia` (en)</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
@@ -4497,251 +5052,256 @@
           <t>`assingments` (en)</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>assignments</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G119"/>
+  <autoFilter ref="A1:H119"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlforma